--- a/MATH/M01/bus123-math-m01-l01-starter.xlsx
+++ b/MATH/M01/bus123-math-m01-l01-starter.xlsx
@@ -2,11 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rae060105bf99445c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R15f00056bade4c20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R3603659e9e894627"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R88ad6bdf8bcc4e85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R3f641ab9d6fd462d" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R8d79c5d7ed6442fe" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R7a7fe7b63d4740be" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R0d3232f2106d47d1" state="visible"/>
   </x:sheets>
+  <x:calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </x:workbook>
 </file>
 
@@ -16,7 +17,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="12">
+  <x:numFmts count="5">
+    <x:numFmt numFmtId="200" formatCode="#,##0"/>
+    <x:numFmt numFmtId="201" formatCode="$#,##0"/>
+    <x:numFmt numFmtId="202" formatCode="General"/>
+    <x:numFmt numFmtId="203" formatCode="0.00%"/>
+    <x:numFmt numFmtId="204" formatCode="@"/>
+  </x:numFmts>
+  <x:fonts count="14">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -86,8 +94,19 @@
       <x:color rgb="FF355773"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Aptos"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="20">
+  <x:fills count="24">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -172,6 +191,26 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2EEE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0E1116"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFAF8F3"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -282,7 +321,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="62">
+  <x:cellXfs count="101">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -427,11 +466,116 @@
     <x:xf numFmtId="0" fontId="6" fillId="19" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="4" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="7" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="4">
+  <x:dxfs count="7">
     <x:dxf>
       <x:fill>
         <x:patternFill>
@@ -457,6 +601,27 @@
       <x:fill>
         <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -790,10 +955,8 @@
           <x:t xml:space="preserve">2</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use the Live You Try It tab when the deck pauses. The yellow cells are yours.</x:t>
-        </x:is>
+      <x:c r="B8" s="21" t="str">
+        <x:v>At slides 9, 14 and 20: predict in HTML, build in Excel, then explain. Yellow cells are yours.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="20" customFormat="1" ht="24" customHeight="1">
@@ -808,16 +971,14 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="10" s="20" customFormat="1" ht="24" customHeight="1">
+    <x:row r="10" s="20" customFormat="1" ht="42" customHeight="1">
       <x:c r="A10" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">4</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" s="21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Feedback is gentle: Correct, Try again, or Check formula. The goal is practice, not grading.</x:t>
-        </x:is>
+      <x:c r="B10" s="21" t="str">
+        <x:v>Feedback checks values and formula presence. Check input references in the formula bar and inspect the requested number format yourself.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="20" customFormat="1" ht="24" customHeight="1">
@@ -857,16 +1018,14 @@
       <x:c r="G16" s="2" t="n"/>
       <x:c r="H16" s="2" t="n"/>
     </x:row>
-    <x:row r="17" s="20" customFormat="1" ht="34" customHeight="1">
+    <x:row r="17" s="20" customFormat="1" ht="40" customHeight="1">
       <x:c r="A17" s="22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Live You Try It</x:t>
         </x:is>
       </x:c>
-      <x:c r="B17" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Matches the slide deck micro-pauses exactly: whole numbers, fractions, and percents.</x:t>
-        </x:is>
+      <x:c r="B17" s="22" t="str">
+        <x:v>Slide 9: E6:E8. Slide 14: E10:E12. Slide 20: E14:E16. Complete each block, including its yes/no reflection.</x:v>
       </x:c>
       <x:c r="C17" s="23" t="n"/>
       <x:c r="D17" s="23" t="n"/>
@@ -881,10 +1040,8 @@
           <x:t xml:space="preserve">Class Challenge</x:t>
         </x:is>
       </x:c>
-      <x:c r="B18" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A richer next-class workshop that extends the same Meridian numbers into a multi-step model.</x:t>
-        </x:is>
+      <x:c r="B18" s="25" t="str">
+        <x:v>Build the linked model first. Later, use the reference-copying workshop at the bottom of Class Challenge.</x:v>
       </x:c>
       <x:c r="C18" s="23" t="n"/>
       <x:c r="D18" s="23" t="n"/>
@@ -957,6 +1114,7 @@
     <x:col min="5" max="6" width="18" style="20" customWidth="1"/>
     <x:col min="7" max="7" width="31" style="20" customWidth="1"/>
     <x:col min="8" max="8" width="14" style="20" customWidth="1"/>
+    <x:col min="6" max="6" width="27" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="20" customFormat="1" ht="30" customHeight="1">
@@ -968,7 +1126,7 @@
     </x:row>
     <x:row r="2" s="20" customFormat="1" ht="16" customHeight="1">
       <x:c r="A2" s="30" t="str">
-        <x:v>Type formulas in yellow cells, then apply the number format shown on the slide.</x:v>
+        <x:v>Predict in HTML → calculate in yellow cells → check references and format → explain.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="20" customFormat="1" ht="32" customHeight="1">
@@ -1013,16 +1171,14 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="6" s="20" customFormat="1" ht="40" customHeight="1">
+    <x:row r="6" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A6" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">09</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Whole Numbers 1: New account count</x:t>
-        </x:is>
+      <x:c r="B6" s="15" t="str">
+        <x:v>New account count: starting accounts minus lost accounts</x:v>
       </x:c>
       <x:c r="C6" s="15" t="n">
         <x:v>57</x:v>
@@ -1030,55 +1186,49 @@
       <x:c r="D6" s="15" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E6" s="16" t="n"/>
-      <x:c r="F6" s="6" t="str">
-        <x:f>IF(E6="","",IF(ABS(E6-(C6-D6))&lt;0.0001,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G6" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">'=starting accounts - lost accounts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H6" s="15" t="inlineStr">
+      <x:c r="E6" s="62"/>
+      <x:c r="F6" s="68" t="str">
+        <x:f>IFERROR(IF(E6="","",IF(NOT(IFERROR(ISFORMULA(E6),TRUE)),"Enter a formula",IF(ABS(E6-(C6-D6))&lt;0.0001,"Value OK; check refs/format","Try again"))),"Check formula / inputs")</x:f>
+      </x:c>
+      <x:c r="G6" s="69" t="str">
+        <x:v>Subtract lost accounts from starting accounts.</x:v>
+      </x:c>
+      <x:c r="H6" s="70" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Subtract</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="7" s="20" customFormat="1" ht="40" customHeight="1">
+    <x:row r="7" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A7" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">09</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Whole Numbers 2: New quarterly fee revenue</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="17" t="n">
-        <x:f>E6</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="n">
+      <x:c r="B7" s="17" t="str">
+        <x:v>New quarterly revenue: accounts × fee/account/quarter</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="str">
+        <x:f>IF(E6="","",E6)</x:f>
+      </x:c>
+      <x:c r="D7" s="63" t="n">
         <x:v>4200</x:v>
       </x:c>
-      <x:c r="E7" s="16" t="n"/>
-      <x:c r="F7" s="6" t="str">
-        <x:f>IF(E7="","",IF(ABS(E7-(E6*D7))&lt;0.01,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G7" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">'=new accounts * fee per account</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H7" s="17" t="inlineStr">
+      <x:c r="E7" s="65"/>
+      <x:c r="F7" s="68" t="str">
+        <x:f>IFERROR(IF(AND(LEFT(F6,8)="Value OK"),IF(E7="","",IF(NOT(IFERROR(ISFORMULA(E7),TRUE)),"Enter a formula",IF(ABS(E7-(C7*D7))&lt;0.01,"Value OK; check refs/format","Try again"))),"Complete E6 first"),"Check formula / inputs")</x:f>
+        <x:v>Complete E6 first</x:v>
+      </x:c>
+      <x:c r="G7" s="71" t="str">
+        <x:v>Use the linked count in C7 and quarterly fee in D7.</x:v>
+      </x:c>
+      <x:c r="H7" s="72" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Multiply</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="8" s="20" customFormat="1" ht="40" customHeight="1">
+    <x:row r="8" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A8" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">09</x:t>
@@ -1091,23 +1241,28 @@
       </x:c>
       <x:c r="C8" s="15" t="n"/>
       <x:c r="D8" s="15" t="n"/>
-      <x:c r="E8" s="5" t="n"/>
-      <x:c r="F8" s="6" t="str">
-        <x:f>IF(E8="","",IF(OR(LOWER(E8)="yes",LOWER(E8)="y"),"Correct","Check formula"))</x:f>
-      </x:c>
-      <x:c r="G8" s="7" t="inlineStr">
+      <x:c r="E8" s="5"/>
+      <x:c r="F8" s="68" t="str">
+        <x:f>IFERROR(IF(AND(LEFT(F6,8)="Value OK",LEFT(F7,8)="Value OK"),IF(E8="","",IF(OR(LOWER(TRIM(E8))=IF(E7&lt;C6*D7,"yes","no"),LOWER(TRIM(E8))=IF(E7&lt;C6*D7,"y","n")),"Reasoning OK; explain why","Compare the results")),"Complete E6, E7 first"),"Check earlier formulas")</x:f>
+        <x:v>Complete E6, E7 first</x:v>
+      </x:c>
+      <x:c r="G8" s="69" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Answer yes/no after comparing to prior revenue</x:t>
         </x:is>
       </x:c>
-      <x:c r="H8" s="15" t="inlineStr">
+      <x:c r="H8" s="70" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Interpret</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="9" s="20" customFormat="1" ht="10" customHeight="1"/>
-    <x:row r="10" s="20" customFormat="1" ht="40" customHeight="1">
+    <x:row r="9" s="20" customFormat="1" ht="48" customHeight="1">
+      <x:c r="F9" s="73"/>
+      <x:c r="G9" s="73"/>
+      <x:c r="H9" s="73"/>
+    </x:row>
+    <x:row r="10" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A10" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">14</x:t>
@@ -1122,25 +1277,25 @@
       <x:c r="D10" s="15" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E10" s="16" t="n"/>
-      <x:c r="F10" s="6" t="str">
-        <x:f>IF(E10="","",IF(ABS(E10-(C10/D10))&lt;0.0001,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G10" s="7" t="str">
-        <x:v>=part / whole, then choose Fraction</x:v>
-      </x:c>
-      <x:c r="H10" s="15" t="str">
+      <x:c r="E10" s="66"/>
+      <x:c r="F10" s="68" t="str">
+        <x:f>IFERROR(IF(E10="","",IF(NOT(IFERROR(ISFORMULA(E10),TRUE)),"Enter a formula",IF(ABS(E10-(C10/D10))&lt;0.0001,"Value OK; check refs/format","Try again"))),"Check formula / inputs")</x:f>
+      </x:c>
+      <x:c r="G10" s="69" t="str">
+        <x:v>Divide this row’s part by whole. Apply Fraction format.</x:v>
+      </x:c>
+      <x:c r="H10" s="70" t="str">
         <x:v>Fraction format</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" s="20" customFormat="1" ht="40" customHeight="1">
+    <x:row r="11" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A11" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">14</x:t>
         </x:is>
       </x:c>
       <x:c r="B11" s="17" t="str">
-        <x:v>Fractions 2: Same formula — format as Percentage</x:v>
+        <x:v>Same part ÷ whole pattern, using row 11 inputs</x:v>
       </x:c>
       <x:c r="C11" s="17" t="n">
         <x:v>5</x:v>
@@ -1148,18 +1303,18 @@
       <x:c r="D11" s="35" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E11" s="10" t="n"/>
-      <x:c r="F11" s="6" t="str">
-        <x:f>IF(E11="","",IF(ABS(E11-(C11/D11))&lt;0.0001,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G11" s="8" t="str">
-        <x:v>=part / whole, then choose Percentage</x:v>
-      </x:c>
-      <x:c r="H11" s="17" t="str">
+      <x:c r="E11" s="66"/>
+      <x:c r="F11" s="68" t="str">
+        <x:f>IFERROR(IF(E11="","",IF(NOT(IFERROR(ISFORMULA(E11),TRUE)),"Enter a formula",IF(ABS(E11-(C11/D11))&lt;0.0001,"Value OK; check refs/format","Try again"))),"Check formula / inputs")</x:f>
+      </x:c>
+      <x:c r="G11" s="71" t="str">
+        <x:v>Use row 11 inputs. Apply Percentage, 1 decimal place.</x:v>
+      </x:c>
+      <x:c r="H11" s="72" t="str">
         <x:v>Percent format</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" s="20" customFormat="1" ht="40" customHeight="1">
+    <x:row r="12" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A12" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">14</x:t>
@@ -1170,85 +1325,82 @@
       </x:c>
       <x:c r="C12" s="15" t="n"/>
       <x:c r="D12" s="15" t="n"/>
-      <x:c r="E12" s="5" t="n"/>
-      <x:c r="F12" s="6" t="str">
-        <x:f>IF(E12="","",IF(OR(LOWER(E12)="yes",LOWER(E12)="y"),"Correct","Check denominator"))</x:f>
-      </x:c>
-      <x:c r="G12" s="7" t="str">
+      <x:c r="E12" s="5"/>
+      <x:c r="F12" s="68" t="str">
+        <x:f>IFERROR(IF(AND(LEFT(F10,8)="Value OK",LEFT(F11,8)="Value OK"),IF(E12="","",IF(OR(LOWER(TRIM(E12))=IF(D10&lt;&gt;6,"yes","no"),LOWER(TRIM(E12))=IF(D10&lt;&gt;6,"y","n")),"Reasoning OK; explain why","Compare the results")),"Complete E10, E11 first"),"Check earlier formulas")</x:f>
+        <x:v>Complete E10, E11 first</x:v>
+      </x:c>
+      <x:c r="G12" s="69" t="str">
         <x:v>Answer yes/no after comparing the before and after teams</x:v>
       </x:c>
-      <x:c r="H12" s="15" t="inlineStr">
+      <x:c r="H12" s="70" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Interpret</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="13" s="20" customFormat="1" ht="10" customHeight="1"/>
-    <x:row r="14" s="20" customFormat="1" ht="40" customHeight="1">
+    <x:row r="13" s="20" customFormat="1" ht="48" customHeight="1">
+      <x:c r="F13" s="73"/>
+      <x:c r="G13" s="73"/>
+      <x:c r="H13" s="73"/>
+    </x:row>
+    <x:row r="14" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A14" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">20</x:t>
         </x:is>
       </x:c>
-      <x:c r="B14" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Percents 1: 12% growth target</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="15" t="n">
+      <x:c r="B14" s="15" t="str">
+        <x:v>Separate scenario: target quarterly revenue after 12% growth</x:v>
+      </x:c>
+      <x:c r="C14" s="64" t="n">
         <x:v>239400</x:v>
       </x:c>
       <x:c r="D14" s="18" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="E14" s="16" t="n"/>
-      <x:c r="F14" s="6" t="str">
-        <x:f>IF(E14="","",IF(ABS(E14-(C14*(1+D14)))&lt;0.01,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G14" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">'=base * (1 + rate)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H14" s="15" t="inlineStr">
+      <x:c r="E14" s="65"/>
+      <x:c r="F14" s="68" t="str">
+        <x:f>IFERROR(IF(E14="","",IF(NOT(IFERROR(ISFORMULA(E14),TRUE)),"Enter a formula",IF(ABS(E14-(C14*(1+D14)))&lt;0.01,"Value OK; check refs/format","Try again"))),"Check formula / inputs")</x:f>
+      </x:c>
+      <x:c r="G14" s="69" t="str">
+        <x:v>Return to the original $239,400 base; find total target fees, not just the increase.</x:v>
+      </x:c>
+      <x:c r="H14" s="70" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Growth target</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="15" s="20" customFormat="1" ht="40" customHeight="1">
+    <x:row r="15" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A15" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">20</x:t>
         </x:is>
       </x:c>
-      <x:c r="B15" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Percents 2: Actual % change</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="17" t="n">
+      <x:c r="B15" s="17" t="str">
+        <x:v>Actual growth from the older quarterly fee base</x:v>
+      </x:c>
+      <x:c r="C15" s="63" t="n">
         <x:v>239400</x:v>
       </x:c>
-      <x:c r="D15" s="17" t="n">
+      <x:c r="D15" s="63" t="n">
         <x:v>268200</x:v>
       </x:c>
-      <x:c r="E15" s="10" t="n"/>
-      <x:c r="F15" s="6" t="str">
-        <x:f>IF(E15="","",IF(ABS(E15-((D15-C15)/C15))&lt;0.0002,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G15" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">'=(new - old) / old</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H15" s="17" t="inlineStr">
+      <x:c r="E15" s="67"/>
+      <x:c r="F15" s="68" t="str">
+        <x:f>IFERROR(IF(E15="","",IF(NOT(IFERROR(ISFORMULA(E15),TRUE)),"Enter a formula",IF(ABS(E15-((D15-C15)/C15))&lt;0.000001,"Value OK; check refs/format","Try again"))),"Check formula / inputs")</x:f>
+      </x:c>
+      <x:c r="G15" s="71" t="str">
+        <x:v>Subtract old from new, divide by old. Percentage, 2 decimals.</x:v>
+      </x:c>
+      <x:c r="H15" s="72" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Percent change</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="16" s="20" customFormat="1" ht="40" customHeight="1">
+    <x:row r="16" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A16" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">20</x:t>
@@ -1261,16 +1413,15 @@
       </x:c>
       <x:c r="C16" s="15" t="n"/>
       <x:c r="D16" s="15" t="n"/>
-      <x:c r="E16" s="5" t="n"/>
-      <x:c r="F16" s="6" t="str">
-        <x:f>IF(E16="","",IF(OR(LOWER(E16)="yes",LOWER(E16)="y"),"Correct","Check target vs actual"))</x:f>
-      </x:c>
-      <x:c r="G16" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Answer yes/no after comparing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H16" s="15" t="inlineStr">
+      <x:c r="E16" s="5"/>
+      <x:c r="F16" s="68" t="str">
+        <x:f>IFERROR(IF(AND(LEFT(F14,8)="Value OK",LEFT(F15,8)="Value OK"),IF(E16="","",IF(OR(LOWER(TRIM(E16))=IF(D15&gt;E14,"yes","no"),LOWER(TRIM(E16))=IF(D15&gt;E14,"y","n")),"Reasoning OK; explain why","Compare the results")),"Complete E14, E15 first"),"Check earlier formulas")</x:f>
+        <x:v>Complete E14, E15 first</x:v>
+      </x:c>
+      <x:c r="G16" s="69" t="str">
+        <x:v>Compare actual fees in D15 with target E14; explain the dollar gap.</x:v>
+      </x:c>
+      <x:c r="H16" s="70" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Interpret</x:t>
         </x:is>
@@ -1284,28 +1435,26 @@
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">When the slide says You Try It, complete only the matching slide-number block. Use formulas where the prompt asks for a calculation; short yes/no interpretation checks can be typed as words.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B20" s="36" t="n"/>
-      <x:c r="C20" s="36" t="n"/>
-      <x:c r="D20" s="36" t="n"/>
-      <x:c r="E20" s="36" t="n"/>
-      <x:c r="F20" s="36" t="n"/>
-      <x:c r="G20" s="36" t="n"/>
-      <x:c r="H20" s="37" t="n"/>
+      <x:c r="A20" s="74" t="str">
+        <x:v>Value OK means the number is right and a formula is present. Inspect references (a formula can still hardcode inputs) and formatting. Complete E8, E12 and E16, then explain your conclusion to a partner.</x:v>
+      </x:c>
+      <x:c r="B20" s="75" t="n"/>
+      <x:c r="C20" s="75" t="n"/>
+      <x:c r="D20" s="75" t="n"/>
+      <x:c r="E20" s="75" t="n"/>
+      <x:c r="F20" s="75" t="n"/>
+      <x:c r="G20" s="75" t="n"/>
+      <x:c r="H20" s="76" t="n"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="38" t="n"/>
-      <x:c r="B21" s="39" t="n"/>
-      <x:c r="C21" s="39" t="n"/>
-      <x:c r="D21" s="39" t="n"/>
-      <x:c r="E21" s="39" t="n"/>
-      <x:c r="F21" s="39" t="n"/>
-      <x:c r="G21" s="39" t="n"/>
-      <x:c r="H21" s="40" t="n"/>
+      <x:c r="A21" s="77" t="n"/>
+      <x:c r="B21" s="78" t="n"/>
+      <x:c r="C21" s="78" t="n"/>
+      <x:c r="D21" s="78" t="n"/>
+      <x:c r="E21" s="78" t="n"/>
+      <x:c r="F21" s="78" t="n"/>
+      <x:c r="G21" s="78" t="n"/>
+      <x:c r="H21" s="79" t="n"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1315,12 +1464,8 @@
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="F6:F16">
-    <x:cfRule type="expression" dxfId="1" priority="1">
-      <x:formula>ISNUMBER(SEARCH("Correct",F6))</x:formula>
-    </x:cfRule>
-    <x:cfRule type="expression" dxfId="0" priority="2">
-      <x:formula>OR(ISNUMBER(SEARCH("Try",F6)),ISNUMBER(SEARCH("Check",F6)))</x:formula>
-    </x:cfRule>
+    <x:cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Try again"/>
+    <x:cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Check formula"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
     <x:dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="E8 E12 E16">
@@ -1338,9 +1483,10 @@
     <x:col min="1" max="1" width="12" style="20" customWidth="1"/>
     <x:col min="2" max="2" width="42" style="20" customWidth="1"/>
     <x:col min="3" max="5" width="18" style="20" customWidth="1"/>
-    <x:col min="6" max="6" width="24" style="20" customWidth="1"/>
+    <x:col min="6" max="6" width="27" style="20" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="28" style="20" customWidth="1"/>
     <x:col min="8" max="8" width="16" style="20" customWidth="1"/>
+    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="20" customFormat="1" ht="30" customHeight="1">
@@ -1380,10 +1526,8 @@
           <x:t xml:space="preserve">Input A</x:t>
         </x:is>
       </x:c>
-      <x:c r="D7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input B</x:t>
-        </x:is>
+      <x:c r="D7" s="2" t="str">
+        <x:v>Input B / Added</x:v>
       </x:c>
       <x:c r="E7" s="2" t="inlineStr">
         <x:is>
@@ -1405,112 +1549,106 @@
           <x:t xml:space="preserve">Skill</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="8" s="20" customFormat="1" ht="42" customHeight="1">
+      <x:c r="I7" s="83" t="str">
+        <x:v>Lost accounts</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A8" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Q1-end accounts from 48 start, +12, -3</x:t>
-        </x:is>
+      <x:c r="B8" s="25" t="str">
+        <x:v>Q1-end accounts: start + added − lost</x:v>
       </x:c>
       <x:c r="C8" s="25" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D8" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">+12 / -3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E8" s="11" t="n"/>
-      <x:c r="F8" s="6" t="str">
-        <x:f>IF(E8="","",IF(ABS(E8-57)&lt;0.0001,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G8" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">What changed from the starting count?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H8" s="25" t="inlineStr">
+      <x:c r="D8" s="25" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E8" s="11"/>
+      <x:c r="F8" s="68" t="str">
+        <x:f>IFERROR(IF(E8="","",IF(NOT(IFERROR(ISFORMULA(E8),TRUE)),"Enter a formula",IF(ABS(E8-(C8+D8-I8))&lt;0.0001,"Value OK; check refs/format","Try again"))),"Check formula / inputs")</x:f>
+      </x:c>
+      <x:c r="G8" s="88" t="str">
+        <x:v>Use C for starting accounts, D for additions, and I for losses.</x:v>
+      </x:c>
+      <x:c r="H8" s="88" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Arithmetic</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="9" s="20" customFormat="1" ht="42" customHeight="1">
+      <x:c r="I8" s="87" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A9" s="22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Q2-end accounts after +7, -2 from Q1-end</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="22" t="n">
-        <x:f>E8</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">+7 / -2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E9" s="11" t="n"/>
-      <x:c r="F9" s="6" t="str">
-        <x:f>IF(E9="","",IF(ABS(E9-(E8+7-2))&lt;0.0001,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G9" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">How does a model reuse prior-period outputs?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H9" s="22" t="inlineStr">
+      <x:c r="B9" s="22" t="str">
+        <x:v>Q2-end accounts: start + added − lost</x:v>
+      </x:c>
+      <x:c r="C9" s="22" t="str">
+        <x:f>IF(E8="","",E8)</x:f>
+      </x:c>
+      <x:c r="D9" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E9" s="11"/>
+      <x:c r="F9" s="68" t="str">
+        <x:f>IFERROR(IF(AND(LEFT(F8,8)="Value OK"),IF(E9="","",IF(NOT(IFERROR(ISFORMULA(E9),TRUE)),"Enter a formula",IF(ABS(E9-(C9+D9-I9))&lt;0.0001,"Value OK; check refs/format","Try again"))),"Complete E8 first"),"Check formula / inputs")</x:f>
+        <x:v>Complete E8 first</x:v>
+      </x:c>
+      <x:c r="G9" s="89" t="str">
+        <x:v>Use C for starting accounts, D for additions, and I for losses.</x:v>
+      </x:c>
+      <x:c r="H9" s="89" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Linked formula</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="10" s="20" customFormat="1" ht="42" customHeight="1">
+      <x:c r="I9" s="87" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A10" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">3</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Q3-end accounts after +5, -1 from Q2-end</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="25" t="n">
-        <x:f>E9</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">+5 / -1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" s="11" t="n"/>
-      <x:c r="F10" s="6" t="str">
-        <x:f>IF(E10="","",IF(ABS(E10-(E9+5-1))&lt;0.0001,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G10" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Why is linking safer than retyping?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H10" s="25" t="inlineStr">
+      <x:c r="B10" s="25" t="str">
+        <x:v>Q3-end accounts: start + added − lost</x:v>
+      </x:c>
+      <x:c r="C10" s="25" t="str">
+        <x:f>IF(E9="","",E9)</x:f>
+      </x:c>
+      <x:c r="D10" s="25" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E10" s="11"/>
+      <x:c r="F10" s="68" t="str">
+        <x:f>IFERROR(IF(AND(LEFT(F9,8)="Value OK"),IF(E10="","",IF(NOT(IFERROR(ISFORMULA(E10),TRUE)),"Enter a formula",IF(ABS(E10-(C10+D10-I10))&lt;0.0001,"Value OK; check refs/format","Try again"))),"Complete E9 first"),"Check formula / inputs")</x:f>
+        <x:v>Complete E9 first</x:v>
+      </x:c>
+      <x:c r="G10" s="88" t="str">
+        <x:v>Use C for starting accounts, D for additions, and I for losses.</x:v>
+      </x:c>
+      <x:c r="H10" s="88" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Linked formula</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="11" s="20" customFormat="1" ht="42" customHeight="1">
+      <x:c r="I10" s="87" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A11" s="22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">4</x:t>
@@ -1525,25 +1663,24 @@
         <x:f>E8</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D11" s="22" t="n">
+      <x:c r="D11" s="91" t="n">
         <x:v>4200</x:v>
       </x:c>
-      <x:c r="E11" s="11" t="n"/>
-      <x:c r="F11" s="6" t="str">
-        <x:f>IF(E11="","",IF(ABS(E11-(E8*D11))&lt;0.01,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G11" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">What unit is the fee rate using?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H11" s="22" t="inlineStr">
+      <x:c r="E11" s="93"/>
+      <x:c r="F11" s="68" t="str">
+        <x:f>IFERROR(IF(AND(LEFT(F8,8)="Value OK"),IF(E11="","",IF(NOT(IFERROR(ISFORMULA(E11),TRUE)),"Enter a formula",IF(ABS(E11-(C11*D11))&lt;0.0001,"Value OK; check refs/format","Try again"))),"Complete E8 first"),"Check formula / inputs")</x:f>
+        <x:v>Complete E8 first</x:v>
+      </x:c>
+      <x:c r="G11" s="89" t="str">
+        <x:v>D11 is the shared quarterly fee assumption.</x:v>
+      </x:c>
+      <x:c r="H11" s="89" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Revenue</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="12" s="20" customFormat="1" ht="42" customHeight="1">
+    <x:row r="12" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A12" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">5</x:t>
@@ -1558,25 +1695,25 @@
         <x:f>E9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D12" s="25" t="n">
+      <x:c r="D12" s="92" t="n">
+        <x:f>$D$11</x:f>
         <x:v>4200</x:v>
       </x:c>
-      <x:c r="E12" s="11" t="n"/>
-      <x:c r="F12" s="6" t="str">
-        <x:f>IF(E12="","",IF(ABS(E12-(E9*D12))&lt;0.01,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G12" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">What would break if the fee were annual?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H12" s="25" t="inlineStr">
+      <x:c r="E12" s="93"/>
+      <x:c r="F12" s="68" t="str">
+        <x:f>IFERROR(IF(AND(LEFT(F9,8)="Value OK"),IF(E12="","",IF(NOT(IFERROR(ISFORMULA(E12),TRUE)),"Enter a formula",IF(ABS(E12-(C12*D12))&lt;0.0001,"Value OK; check refs/format","Try again"))),"Complete E9 first"),"Check formula / inputs")</x:f>
+        <x:v>Complete E9 first</x:v>
+      </x:c>
+      <x:c r="G12" s="88" t="str">
+        <x:v>D12 links to the shared fee in D11.</x:v>
+      </x:c>
+      <x:c r="H12" s="88" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Revenue</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="13" s="20" customFormat="1" ht="42" customHeight="1">
+    <x:row r="13" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A13" s="22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">6</x:t>
@@ -1591,25 +1728,25 @@
         <x:f>E10</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D13" s="22" t="n">
+      <x:c r="D13" s="91" t="n">
+        <x:f>$D$11</x:f>
         <x:v>4200</x:v>
       </x:c>
-      <x:c r="E13" s="11" t="n"/>
-      <x:c r="F13" s="6" t="str">
-        <x:f>IF(E13="","",IF(ABS(E13-(E10*D13))&lt;0.01,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G13" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">What trend do you see?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H13" s="22" t="inlineStr">
+      <x:c r="E13" s="93"/>
+      <x:c r="F13" s="68" t="str">
+        <x:f>IFERROR(IF(AND(LEFT(F10,8)="Value OK"),IF(E13="","",IF(NOT(IFERROR(ISFORMULA(E13),TRUE)),"Enter a formula",IF(ABS(E13-(C13*D13))&lt;0.0001,"Value OK; check refs/format","Try again"))),"Complete E10 first"),"Check formula / inputs")</x:f>
+        <x:v>Complete E10 first</x:v>
+      </x:c>
+      <x:c r="G13" s="89" t="str">
+        <x:v>D13 links to the shared fee in D11.</x:v>
+      </x:c>
+      <x:c r="H13" s="89" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Revenue</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="14" s="20" customFormat="1" ht="42" customHeight="1">
+    <x:row r="14" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A14" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">7</x:t>
@@ -1625,22 +1762,23 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="25" t="n"/>
-      <x:c r="E14" s="11" t="n"/>
-      <x:c r="F14" s="6" t="str">
-        <x:f>IF(E14="","",IF(ABS(E14-SUM(E11:E13))&lt;0.01,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G14" s="25" t="inlineStr">
+      <x:c r="E14" s="93"/>
+      <x:c r="F14" s="68" t="str">
+        <x:f>IFERROR(IF(AND(LEFT(F11,8)="Value OK",LEFT(F12,8)="Value OK",LEFT(F13,8)="Value OK"),IF(E14="","",IF(NOT(IFERROR(ISFORMULA(E14),TRUE)),"Enter a formula",IF(ABS(E14-(SUM(E11:E13)))&lt;0.0001,"Value OK; check refs/format","Try again"))),"Complete E11, E12, E13 first"),"Check formula / inputs")</x:f>
+        <x:v>Complete E11, E12, E13 first</x:v>
+      </x:c>
+      <x:c r="G14" s="88" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Why use SUM instead of adding manually?</x:t>
         </x:is>
       </x:c>
-      <x:c r="H14" s="25" t="inlineStr">
+      <x:c r="H14" s="88" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SUM</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="15" s="20" customFormat="1" ht="42" customHeight="1">
+    <x:row r="15" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A15" s="22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">8</x:t>
@@ -1659,20 +1797,31 @@
         <x:f>E13</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="12" t="n"/>
-      <x:c r="F15" s="6" t="str">
-        <x:f>IF(E15="","",IF(ABS(E15-((E13-E11)/E11))&lt;0.0002,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G15" s="22" t="inlineStr">
+      <x:c r="E15" s="12"/>
+      <x:c r="F15" s="68" t="str">
+        <x:f>IFERROR(IF(AND(LEFT(F11,8)="Value OK",LEFT(F13,8)="Value OK"),IF(E15="","",IF(NOT(IFERROR(ISFORMULA(E15),TRUE)),"Enter a formula",IF(ABS(E15-((D15-C15)/C15))&lt;0.000001,"Value OK; check refs/format","Try again"))),"Complete E11, E13 first"),"Check formula / inputs")</x:f>
+        <x:v>Complete E11, E13 first</x:v>
+      </x:c>
+      <x:c r="G15" s="89" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Which number is the base?</x:t>
         </x:is>
       </x:c>
-      <x:c r="H15" s="22" t="inlineStr">
+      <x:c r="H15" s="89" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Percent change</x:t>
         </x:is>
       </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="F16" s="73"/>
+      <x:c r="G16" s="73"/>
+      <x:c r="H16" s="73"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="F17" s="73"/>
+      <x:c r="G17" s="73"/>
+      <x:c r="H17" s="73"/>
     </x:row>
     <x:row r="18" s="20" customFormat="1" ht="24" customHeight="1">
       <x:c r="A18" s="27" t="inlineStr">
@@ -1680,6 +1829,14 @@
           <x:t xml:space="preserve">Challenge 2 — Service-Line Mix</x:t>
         </x:is>
       </x:c>
+      <x:c r="F18" s="73"/>
+      <x:c r="G18" s="73"/>
+      <x:c r="H18" s="73"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="F19" s="73"/>
+      <x:c r="G19" s="73"/>
+      <x:c r="H19" s="73"/>
     </x:row>
     <x:row r="20" s="20" customFormat="1" ht="28" customHeight="1">
       <x:c r="A20" s="2" t="inlineStr">
@@ -1707,23 +1864,23 @@
           <x:t xml:space="preserve">Formula / Answer</x:t>
         </x:is>
       </x:c>
-      <x:c r="F20" s="2" t="inlineStr">
+      <x:c r="F20" s="90" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Coach Check</x:t>
         </x:is>
       </x:c>
-      <x:c r="G20" s="2" t="inlineStr">
+      <x:c r="G20" s="90" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Interpretation Prompt</x:t>
         </x:is>
       </x:c>
-      <x:c r="H20" s="2" t="inlineStr">
+      <x:c r="H20" s="90" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Skill</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="21" s="20" customFormat="1" ht="42" customHeight="1">
+    <x:row r="21" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A21" s="22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1</x:t>
@@ -1738,22 +1895,22 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="D21" s="22" t="n"/>
-      <x:c r="E21" s="11" t="n"/>
-      <x:c r="F21" s="6" t="str">
-        <x:f>IF(E21="","",IF(ABS(E21-57)&lt;0.0001,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G21" s="22" t="inlineStr">
+      <x:c r="E21" s="11"/>
+      <x:c r="F21" s="68" t="str">
+        <x:f>IFERROR(IF(E21="","",IF(NOT(IFERROR(ISFORMULA(E21),TRUE)),"Enter a formula",IF(ABS(E21-(C21))&lt;0.0001,"Value OK; check refs/format","Try again"))),"Check formula / inputs")</x:f>
+      </x:c>
+      <x:c r="G21" s="89" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Use this total for the first mix checks.</x:t>
         </x:is>
       </x:c>
-      <x:c r="H21" s="22" t="inlineStr">
+      <x:c r="H21" s="89" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Input</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="22" s="20" customFormat="1" ht="42" customHeight="1">
+    <x:row r="22" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A22" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2</x:t>
@@ -1771,22 +1928,23 @@
         <x:f>E21</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="12" t="n"/>
-      <x:c r="F22" s="6" t="str">
-        <x:f>IF(E22="","",IF(ABS(E22-(C22/D22))&lt;0.0002,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G22" s="25" t="inlineStr">
+      <x:c r="E22" s="12"/>
+      <x:c r="F22" s="68" t="str">
+        <x:f>IFERROR(IF(AND(LEFT(F21,8)="Value OK"),IF(E22="","",IF(NOT(IFERROR(ISFORMULA(E22),TRUE)),"Enter a formula",IF(ABS(E22-(C22/D22))&lt;0.000001,"Value OK; check refs/format","Try again"))),"Complete E21 first"),"Check formula / inputs")</x:f>
+        <x:v>Complete E21 first</x:v>
+      </x:c>
+      <x:c r="G22" s="88" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Format as Percentage.</x:t>
         </x:is>
       </x:c>
-      <x:c r="H22" s="25" t="inlineStr">
+      <x:c r="H22" s="88" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Ratio as %</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="23" s="20" customFormat="1" ht="42" customHeight="1">
+    <x:row r="23" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A23" s="22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">3</x:t>
@@ -1804,22 +1962,23 @@
         <x:f>E21</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="12" t="n"/>
-      <x:c r="F23" s="6" t="str">
-        <x:f>IF(E23="","",IF(ABS(E23-(C23/D23))&lt;0.0002,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G23" s="22" t="inlineStr">
+      <x:c r="E23" s="12"/>
+      <x:c r="F23" s="68" t="str">
+        <x:f>IFERROR(IF(AND(LEFT(F21,8)="Value OK"),IF(E23="","",IF(NOT(IFERROR(ISFORMULA(E23),TRUE)),"Enter a formula",IF(ABS(E23-(C23/D23))&lt;0.000001,"Value OK; check refs/format","Try again"))),"Complete E21 first"),"Check formula / inputs")</x:f>
+        <x:v>Complete E21 first</x:v>
+      </x:c>
+      <x:c r="G23" s="89" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Is this a change or a share?</x:t>
         </x:is>
       </x:c>
-      <x:c r="H23" s="22" t="inlineStr">
+      <x:c r="H23" s="89" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Ratio as %</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="24" s="20" customFormat="1" ht="42" customHeight="1">
+    <x:row r="24" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A24" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">4</x:t>
@@ -1837,22 +1996,23 @@
         <x:f>E21</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="12" t="n"/>
-      <x:c r="F24" s="6" t="str">
-        <x:f>IF(E24="","",IF(ABS(E24-(C24/D24))&lt;0.0002,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G24" s="25" t="inlineStr">
+      <x:c r="E24" s="12"/>
+      <x:c r="F24" s="68" t="str">
+        <x:f>IFERROR(IF(AND(LEFT(F21,8)="Value OK"),IF(E24="","",IF(NOT(IFERROR(ISFORMULA(E24),TRUE)),"Enter a formula",IF(ABS(E24-(C24/D24))&lt;0.000001,"Value OK; check refs/format","Try again"))),"Complete E21 first"),"Check formula / inputs")</x:f>
+        <x:v>Complete E21 first</x:v>
+      </x:c>
+      <x:c r="G24" s="88" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Combine parts before dividing by whole.</x:t>
         </x:is>
       </x:c>
-      <x:c r="H24" s="25" t="inlineStr">
+      <x:c r="H24" s="88" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Ratio as %</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="25" s="20" customFormat="1" ht="42" customHeight="1">
+    <x:row r="25" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A25" s="22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">5</x:t>
@@ -1869,22 +2029,22 @@
       <x:c r="D25" s="9" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="E25" s="11" t="n"/>
-      <x:c r="F25" s="6" t="str">
-        <x:f>IF(E25="","",IF(ABS(E25-(C25*(1+D25)))&lt;0.01,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G25" s="22" t="inlineStr">
+      <x:c r="E25" s="11"/>
+      <x:c r="F25" s="68" t="str">
+        <x:f>IFERROR(IF(E25="","",IF(NOT(IFERROR(ISFORMULA(E25),TRUE)),"Enter a formula",IF(ABS(E25-(C25*(1+D25)))&lt;0.0001,"Value OK; check refs/format","Try again"))),"Check formula / inputs")</x:f>
+      </x:c>
+      <x:c r="G25" s="89" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Should client counts be rounded for a final business recommendation?</x:t>
         </x:is>
       </x:c>
-      <x:c r="H25" s="22" t="inlineStr">
+      <x:c r="H25" s="89" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Growth</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="26" s="20" customFormat="1" ht="42" customHeight="1">
+    <x:row r="26" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A26" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">6</x:t>
@@ -1902,22 +2062,23 @@
         <x:f>E25</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E26" s="11" t="n"/>
-      <x:c r="F26" s="6" t="str">
-        <x:f>IF(E26="","",IF(ABS(E26-(C26+D26))&lt;0.01,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G26" s="25" t="inlineStr">
+      <x:c r="E26" s="11"/>
+      <x:c r="F26" s="68" t="str">
+        <x:f>IFERROR(IF(AND(LEFT(F25,8)="Value OK"),IF(E26="","",IF(NOT(IFERROR(ISFORMULA(E26),TRUE)),"Enter a formula",IF(ABS(E26-(C26+D26))&lt;0.0001,"Value OK; check refs/format","Try again"))),"Complete E25 first"),"Check formula / inputs")</x:f>
+        <x:v>Complete E25 first</x:v>
+      </x:c>
+      <x:c r="G26" s="88" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Old tax + estate plus new investment count.</x:t>
         </x:is>
       </x:c>
-      <x:c r="H26" s="25" t="inlineStr">
+      <x:c r="H26" s="88" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Total</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="27" s="20" customFormat="1" ht="42" customHeight="1">
+    <x:row r="27" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A27" s="22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">7</x:t>
@@ -1936,22 +2097,23 @@
         <x:f>E26</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="12" t="n"/>
-      <x:c r="F27" s="6" t="str">
-        <x:f>IF(E27="","",IF(ABS(E27-(C27/D27))&lt;0.0002,"Correct","Try again"))</x:f>
-      </x:c>
-      <x:c r="G27" s="22" t="inlineStr">
+      <x:c r="E27" s="12"/>
+      <x:c r="F27" s="68" t="str">
+        <x:f>IFERROR(IF(AND(LEFT(F25,8)="Value OK",LEFT(F26,8)="Value OK"),IF(E27="","",IF(NOT(IFERROR(ISFORMULA(E27),TRUE)),"Enter a formula",IF(ABS(E27-(C27/D27))&lt;0.000001,"Value OK; check refs/format","Try again"))),"Complete E25, E26 first"),"Check formula / inputs")</x:f>
+        <x:v>Complete E25, E26 first</x:v>
+      </x:c>
+      <x:c r="G27" s="89" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">How did the mix change?</x:t>
         </x:is>
       </x:c>
-      <x:c r="H27" s="22" t="inlineStr">
+      <x:c r="H27" s="89" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Ratio as %</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="28" s="20" customFormat="1" ht="42" customHeight="1">
+    <x:row r="28" s="20" customFormat="1" ht="48" customHeight="1">
       <x:c r="A28" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">8</x:t>
@@ -1964,18 +2126,118 @@
       </x:c>
       <x:c r="C28" s="25" t="n"/>
       <x:c r="D28" s="25" t="n"/>
-      <x:c r="E28" s="11" t="n"/>
-      <x:c r="F28" s="6" t="n"/>
-      <x:c r="G28" s="25" t="inlineStr">
+      <x:c r="E28" s="11"/>
+      <x:c r="F28" s="68" t="n"/>
+      <x:c r="G28" s="88" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Explain what changed in the service-line mix.</x:t>
         </x:is>
       </x:c>
-      <x:c r="H28" s="25" t="inlineStr">
+      <x:c r="H28" s="88" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Interpret</x:t>
         </x:is>
       </x:c>
+    </x:row>
+    <x:row r="30" ht="26" customHeight="1">
+      <x:c r="A30" s="94" t="str">
+        <x:v>Later workshop · Copy formulas, then explain which references move</x:v>
+      </x:c>
+      <x:c r="B30" s="94"/>
+      <x:c r="C30" s="94"/>
+      <x:c r="D30" s="94"/>
+      <x:c r="E30" s="94"/>
+      <x:c r="F30" s="94"/>
+      <x:c r="G30" s="94"/>
+      <x:c r="H30" s="94"/>
+    </x:row>
+    <x:row r="32" ht="24" customHeight="1">
+      <x:c r="A32" s="95" t="str">
+        <x:v>1 · Relative: enter =C11*D11 in E11 and fill through E13. Both input references move down one row.</x:v>
+      </x:c>
+      <x:c r="B32" s="95"/>
+      <x:c r="C32" s="95"/>
+      <x:c r="D32" s="95"/>
+      <x:c r="E32" s="95"/>
+      <x:c r="F32" s="95"/>
+      <x:c r="G32" s="95"/>
+      <x:c r="H32" s="95"/>
+    </x:row>
+    <x:row r="33" ht="24" customHeight="1">
+      <x:c r="A33" s="95"/>
+      <x:c r="B33" s="95"/>
+      <x:c r="C33" s="95"/>
+      <x:c r="D33" s="95"/>
+      <x:c r="E33" s="95"/>
+      <x:c r="F33" s="95"/>
+      <x:c r="G33" s="95"/>
+      <x:c r="H33" s="95"/>
+    </x:row>
+    <x:row r="34" ht="24" customHeight="1">
+      <x:c r="A34" s="95" t="str">
+        <x:v>2 · Absolute: use =C22/$E$21 in E22, then fill to E23. The service-line count moves; total clients stays fixed.</x:v>
+      </x:c>
+      <x:c r="B34" s="95"/>
+      <x:c r="C34" s="95"/>
+      <x:c r="D34" s="95"/>
+      <x:c r="E34" s="95"/>
+      <x:c r="F34" s="95"/>
+      <x:c r="G34" s="95"/>
+      <x:c r="H34" s="95"/>
+    </x:row>
+    <x:row r="35" ht="24" customHeight="1">
+      <x:c r="A35" s="95"/>
+      <x:c r="B35" s="95"/>
+      <x:c r="C35" s="95"/>
+      <x:c r="D35" s="95"/>
+      <x:c r="E35" s="95"/>
+      <x:c r="F35" s="95"/>
+      <x:c r="G35" s="95"/>
+      <x:c r="H35" s="95"/>
+    </x:row>
+    <x:row r="36" ht="24" customHeight="1">
+      <x:c r="A36" s="95" t="str">
+        <x:v>3 · Shared fee: use =C11*$D$11 in E11 and fill through E13. Change D11 temporarily; all quarterly revenues should update. Restore $4,200.</x:v>
+      </x:c>
+      <x:c r="B36" s="95"/>
+      <x:c r="C36" s="95"/>
+      <x:c r="D36" s="95"/>
+      <x:c r="E36" s="95"/>
+      <x:c r="F36" s="95"/>
+      <x:c r="G36" s="95"/>
+      <x:c r="H36" s="95"/>
+    </x:row>
+    <x:row r="37" ht="24" customHeight="1">
+      <x:c r="A37" s="95"/>
+      <x:c r="B37" s="95"/>
+      <x:c r="C37" s="95"/>
+      <x:c r="D37" s="95"/>
+      <x:c r="E37" s="95"/>
+      <x:c r="F37" s="95"/>
+      <x:c r="G37" s="95"/>
+      <x:c r="H37" s="95"/>
+    </x:row>
+    <x:row r="38" ht="24" customHeight="1">
+      <x:c r="A38" s="95" t="str">
+        <x:v>Explain: which input should move, and which should stay fixed? Mixed references come later, when copying across a two-dimensional table.</x:v>
+      </x:c>
+      <x:c r="B38" s="95"/>
+      <x:c r="C38" s="95"/>
+      <x:c r="D38" s="95"/>
+      <x:c r="E38" s="95"/>
+      <x:c r="F38" s="95"/>
+      <x:c r="G38" s="95"/>
+      <x:c r="H38" s="95"/>
+    </x:row>
+    <x:row r="39" ht="24" customHeight="1">
+      <x:c r="A39" s="95"/>
+      <x:c r="B39" s="95"/>
+      <x:c r="C39" s="95"/>
+      <x:c r="D39" s="95"/>
+      <x:c r="E39" s="95"/>
+      <x:c r="F39" s="95"/>
+      <x:c r="G39" s="95"/>
+      <x:c r="H39" s="95"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1983,14 +2245,14 @@
     <x:mergeCell ref="A2:H2"/>
     <x:mergeCell ref="A5:H5"/>
     <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A30:H30"/>
+    <x:mergeCell ref="A32:H33"/>
+    <x:mergeCell ref="A34:H35"/>
+    <x:mergeCell ref="A36:H37"/>
+    <x:mergeCell ref="A38:H39"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="F8:F27">
-    <x:cfRule type="expression" dxfId="1" priority="1">
-      <x:formula>ISNUMBER(SEARCH("Correct",F8))</x:formula>
-    </x:cfRule>
-    <x:cfRule type="expression" dxfId="0" priority="2">
-      <x:formula>OR(ISNUMBER(SEARCH("Try",F8)),ISNUMBER(SEARCH("Check",F8)))</x:formula>
-    </x:cfRule>
+    <x:cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Try again"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2138,10 +2400,76 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="7" s="20" customFormat="1" ht="34" customHeight="1"/>
-    <x:row r="8" s="20" customFormat="1" ht="34" customHeight="1"/>
-    <x:row r="9" s="20" customFormat="1" ht="34" customHeight="1"/>
-    <x:row r="11" s="20" customFormat="1" ht="24" customHeight="1"/>
+    <x:row r="7" s="20" customFormat="1" ht="40" customHeight="1">
+      <x:c r="A7" s="95" t="str">
+        <x:v>Percent of a whole</x:v>
+      </x:c>
+      <x:c r="B7" s="100" t="str">
+        <x:v>=whole*rate</x:v>
+      </x:c>
+      <x:c r="C7" s="95" t="str">
+        <x:v>Find the increase amount or part.</x:v>
+      </x:c>
+      <x:c r="D7" s="99" t="str">
+        <x:v>A dollar whole gives a dollar result.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" s="20" customFormat="1" ht="40" customHeight="1">
+      <x:c r="A8" s="95" t="str">
+        <x:v>Growth target</x:v>
+      </x:c>
+      <x:c r="B8" s="100" t="str">
+        <x:v>=base*(1+rate)</x:v>
+      </x:c>
+      <x:c r="C8" s="95" t="str">
+        <x:v>Keep the original base and add its increase.</x:v>
+      </x:c>
+      <x:c r="D8" s="99" t="str">
+        <x:v>Target total differs from increase amount.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" s="20" customFormat="1" ht="40" customHeight="1">
+      <x:c r="A9" s="95" t="str">
+        <x:v>Percent change</x:v>
+      </x:c>
+      <x:c r="B9" s="100" t="str">
+        <x:v>=(new-old)/old</x:v>
+      </x:c>
+      <x:c r="C9" s="95" t="str">
+        <x:v>Compare a later value with its older base.</x:v>
+      </x:c>
+      <x:c r="D9" s="99" t="str">
+        <x:v>Percentage format; never multiply by 100.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="40" customHeight="1">
+      <x:c r="A10" s="95" t="str">
+        <x:v>Relative reference (later)</x:v>
+      </x:c>
+      <x:c r="B10" s="100" t="str">
+        <x:v>=C11*D11</x:v>
+      </x:c>
+      <x:c r="C10" s="95" t="str">
+        <x:v>Fill down: both row references move.</x:v>
+      </x:c>
+      <x:c r="D10" s="99" t="str">
+        <x:v>Predict the next formula before copying.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" s="20" customFormat="1" ht="40" customHeight="1">
+      <x:c r="A11" s="95" t="str">
+        <x:v>Absolute reference (later)</x:v>
+      </x:c>
+      <x:c r="B11" s="100" t="str">
+        <x:v>=C22/$E$21</x:v>
+      </x:c>
+      <x:c r="C11" s="95" t="str">
+        <x:v>Fill down: E21 remains the shared total.</x:v>
+      </x:c>
+      <x:c r="D11" s="99" t="str">
+        <x:v>The dollar signs fix the address when copying.</x:v>
+      </x:c>
+    </x:row>
     <x:row r="12" s="20" customFormat="1" ht="28" customHeight="1"/>
     <x:row r="13" s="20" customFormat="1" ht="34" customHeight="1"/>
     <x:row r="14" s="20" customFormat="1" ht="34" customHeight="1"/>

--- a/MATH/M01/bus123-math-m01-l01-starter.xlsx
+++ b/MATH/M01/bus123-math-m01-l01-starter.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R3f641ab9d6fd462d" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R8d79c5d7ed6442fe" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R7a7fe7b63d4740be" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R0d3232f2106d47d1" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rc890d777785a4ece" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R1684127f76a84c8e" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R1fcd9b2a988f41f3" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R61f1beff38ca42e1" state="visible"/>
   </x:sheets>
   <x:calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </x:workbook>
@@ -321,7 +321,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="101">
+  <x:cellXfs count="102">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -571,6 +571,7 @@
     <x:xf numFmtId="204" fontId="7" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -606,21 +607,21 @@
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -949,26 +950,24 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="8" s="20" customFormat="1" ht="24" customHeight="1">
+    <x:row r="8" s="20" customFormat="1" ht="42" customHeight="1">
       <x:c r="A8" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2</x:t>
         </x:is>
       </x:c>
       <x:c r="B8" s="21" t="str">
-        <x:v>At slides 9, 14 and 20: predict in HTML, build in Excel, then explain. Yellow cells are yours.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" s="20" customFormat="1" ht="24" customHeight="1">
+        <x:v>At slides 9, 14 and 20, build the blank Live You Try It sheet using the slide cell maps. Type the labels and numbers yourself.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" s="20" customFormat="1" ht="42" customHeight="1">
       <x:c r="A9" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">3</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" s="21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Type formulas that start with = whenever possible. Use the visible input cells, not hardcoded answers.</x:t>
-        </x:is>
+      <x:c r="B9" s="21" t="str">
+        <x:v>Write your own formulas using cell references. Leave the calculation cells blank until you are ready to solve them.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="20" customFormat="1" ht="42" customHeight="1">
@@ -978,7 +977,7 @@
         </x:is>
       </x:c>
       <x:c r="B10" s="21" t="str">
-        <x:v>Feedback checks values and formula presence. Check input references in the formula bar and inspect the requested number format yourself.</x:v>
+        <x:v>Live You Try It: widen columns, style headers, and choose number formats. Check your work with a partner. Class Challenge retains automatic feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="20" customFormat="1" ht="24" customHeight="1">
@@ -1018,14 +1017,14 @@
       <x:c r="G16" s="2" t="n"/>
       <x:c r="H16" s="2" t="n"/>
     </x:row>
-    <x:row r="17" s="20" customFormat="1" ht="40" customHeight="1">
+    <x:row r="17" s="20" customFormat="1" ht="42" customHeight="1">
       <x:c r="A17" s="22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Live You Try It</x:t>
         </x:is>
       </x:c>
       <x:c r="B17" s="22" t="str">
-        <x:v>Slide 9: E6:E8. Slide 14: E10:E12. Slide 20: E14:E16. Complete each block, including its yes/no reflection.</x:v>
+        <x:v>Start with an empty grid. Slide 9: B5:E8. Slide 14: B9:E12. Slide 20: B13:E16. Save your completed, formatted sheet.</x:v>
       </x:c>
       <x:c r="C17" s="23" t="n"/>
       <x:c r="D17" s="23" t="n"/>
@@ -1108,370 +1107,319 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="17" style="20" customWidth="1"/>
-    <x:col min="2" max="2" width="34" style="20" customWidth="1"/>
+    <x:col min="1" max="1" width="8.430000305175781" style="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="8.430000305175781" style="20" hidden="0" customWidth="1"/>
     <x:col min="3" max="4" width="14" style="20" customWidth="1"/>
     <x:col min="5" max="6" width="18" style="20" customWidth="1"/>
-    <x:col min="7" max="7" width="31" style="20" customWidth="1"/>
-    <x:col min="8" max="8" width="14" style="20" customWidth="1"/>
-    <x:col min="6" max="6" width="27" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="8.430000305175781" style="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="8.430000305175781" style="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8.430000305175781" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8.430000305175781" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.430000305175781" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="8.430000305175781" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" s="20" customFormat="1" ht="30" customHeight="1">
-      <x:c r="A1" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Live You Try It · Match the Slide Numbers</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="2" s="20" customFormat="1" ht="16" customHeight="1">
-      <x:c r="A2" s="30" t="str">
-        <x:v>Predict in HTML → calculate in yellow cells → check references and format → explain.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" s="20" customFormat="1" ht="32" customHeight="1">
-      <x:c r="A5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Slide</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Step</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input A</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input B</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Your Formula / Answer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Feedback</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Formula Hint</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Skill</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="6" s="20" customFormat="1" ht="48" customHeight="1">
-      <x:c r="A6" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">09</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="15" t="str">
-        <x:v>New account count: starting accounts minus lost accounts</x:v>
-      </x:c>
-      <x:c r="C6" s="15" t="n">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D6" s="15" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="62"/>
-      <x:c r="F6" s="68" t="str">
-        <x:f>IFERROR(IF(E6="","",IF(NOT(IFERROR(ISFORMULA(E6),TRUE)),"Enter a formula",IF(ABS(E6-(C6-D6))&lt;0.0001,"Value OK; check refs/format","Try again"))),"Check formula / inputs")</x:f>
-      </x:c>
-      <x:c r="G6" s="69" t="str">
-        <x:v>Subtract lost accounts from starting accounts.</x:v>
-      </x:c>
-      <x:c r="H6" s="70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Subtract</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="7" s="20" customFormat="1" ht="48" customHeight="1">
-      <x:c r="A7" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">09</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="17" t="str">
-        <x:v>New quarterly revenue: accounts × fee/account/quarter</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="str">
-        <x:f>IF(E6="","",E6)</x:f>
-      </x:c>
-      <x:c r="D7" s="63" t="n">
-        <x:v>4200</x:v>
-      </x:c>
-      <x:c r="E7" s="65"/>
-      <x:c r="F7" s="68" t="str">
-        <x:f>IFERROR(IF(AND(LEFT(F6,8)="Value OK"),IF(E7="","",IF(NOT(IFERROR(ISFORMULA(E7),TRUE)),"Enter a formula",IF(ABS(E7-(C7*D7))&lt;0.01,"Value OK; check refs/format","Try again"))),"Complete E6 first"),"Check formula / inputs")</x:f>
-        <x:v>Complete E6 first</x:v>
-      </x:c>
-      <x:c r="G7" s="71" t="str">
-        <x:v>Use the linked count in C7 and quarterly fee in D7.</x:v>
-      </x:c>
-      <x:c r="H7" s="72" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Multiply</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="8" s="20" customFormat="1" ht="48" customHeight="1">
-      <x:c r="A8" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">09</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Whole Numbers 3: Is the new revenue lower than prior $239,400?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="15" t="n"/>
-      <x:c r="D8" s="15" t="n"/>
-      <x:c r="E8" s="5"/>
-      <x:c r="F8" s="68" t="str">
-        <x:f>IFERROR(IF(AND(LEFT(F6,8)="Value OK",LEFT(F7,8)="Value OK"),IF(E8="","",IF(OR(LOWER(TRIM(E8))=IF(E7&lt;C6*D7,"yes","no"),LOWER(TRIM(E8))=IF(E7&lt;C6*D7,"y","n")),"Reasoning OK; explain why","Compare the results")),"Complete E6, E7 first"),"Check earlier formulas")</x:f>
-        <x:v>Complete E6, E7 first</x:v>
-      </x:c>
-      <x:c r="G8" s="69" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Answer yes/no after comparing to prior revenue</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H8" s="70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Interpret</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="9" s="20" customFormat="1" ht="48" customHeight="1">
-      <x:c r="F9" s="73"/>
-      <x:c r="G9" s="73"/>
-      <x:c r="H9" s="73"/>
-    </x:row>
-    <x:row r="10" s="20" customFormat="1" ht="48" customHeight="1">
-      <x:c r="A10" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">14</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" s="15" t="str">
-        <x:v>Fractions 1: New Tax team share — format as Fraction</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E10" s="66"/>
-      <x:c r="F10" s="68" t="str">
-        <x:f>IFERROR(IF(E10="","",IF(NOT(IFERROR(ISFORMULA(E10),TRUE)),"Enter a formula",IF(ABS(E10-(C10/D10))&lt;0.0001,"Value OK; check refs/format","Try again"))),"Check formula / inputs")</x:f>
-      </x:c>
-      <x:c r="G10" s="69" t="str">
-        <x:v>Divide this row’s part by whole. Apply Fraction format.</x:v>
-      </x:c>
-      <x:c r="H10" s="70" t="str">
-        <x:v>Fraction format</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" s="20" customFormat="1" ht="48" customHeight="1">
-      <x:c r="A11" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">14</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="17" t="str">
-        <x:v>Same part ÷ whole pattern, using row 11 inputs</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D11" s="35" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E11" s="66"/>
-      <x:c r="F11" s="68" t="str">
-        <x:f>IFERROR(IF(E11="","",IF(NOT(IFERROR(ISFORMULA(E11),TRUE)),"Enter a formula",IF(ABS(E11-(C11/D11))&lt;0.0001,"Value OK; check refs/format","Try again"))),"Check formula / inputs")</x:f>
-      </x:c>
-      <x:c r="G11" s="71" t="str">
-        <x:v>Use row 11 inputs. Apply Percentage, 1 decimal place.</x:v>
-      </x:c>
-      <x:c r="H11" s="72" t="str">
-        <x:v>Percent format</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" s="20" customFormat="1" ht="48" customHeight="1">
-      <x:c r="A12" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">14</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" s="15" t="str">
-        <x:v>Fractions 3: Did the whole change from 6 to 9?</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="n"/>
-      <x:c r="D12" s="15" t="n"/>
-      <x:c r="E12" s="5"/>
-      <x:c r="F12" s="68" t="str">
-        <x:f>IFERROR(IF(AND(LEFT(F10,8)="Value OK",LEFT(F11,8)="Value OK"),IF(E12="","",IF(OR(LOWER(TRIM(E12))=IF(D10&lt;&gt;6,"yes","no"),LOWER(TRIM(E12))=IF(D10&lt;&gt;6,"y","n")),"Reasoning OK; explain why","Compare the results")),"Complete E10, E11 first"),"Check earlier formulas")</x:f>
-        <x:v>Complete E10, E11 first</x:v>
-      </x:c>
-      <x:c r="G12" s="69" t="str">
-        <x:v>Answer yes/no after comparing the before and after teams</x:v>
-      </x:c>
-      <x:c r="H12" s="70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Interpret</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="13" s="20" customFormat="1" ht="48" customHeight="1">
-      <x:c r="F13" s="73"/>
-      <x:c r="G13" s="73"/>
-      <x:c r="H13" s="73"/>
-    </x:row>
-    <x:row r="14" s="20" customFormat="1" ht="48" customHeight="1">
-      <x:c r="A14" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">20</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" s="15" t="str">
-        <x:v>Separate scenario: target quarterly revenue after 12% growth</x:v>
-      </x:c>
-      <x:c r="C14" s="64" t="n">
-        <x:v>239400</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="n">
-        <x:v>0.12</x:v>
-      </x:c>
-      <x:c r="E14" s="65"/>
-      <x:c r="F14" s="68" t="str">
-        <x:f>IFERROR(IF(E14="","",IF(NOT(IFERROR(ISFORMULA(E14),TRUE)),"Enter a formula",IF(ABS(E14-(C14*(1+D14)))&lt;0.01,"Value OK; check refs/format","Try again"))),"Check formula / inputs")</x:f>
-      </x:c>
-      <x:c r="G14" s="69" t="str">
-        <x:v>Return to the original $239,400 base; find total target fees, not just the increase.</x:v>
-      </x:c>
-      <x:c r="H14" s="70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Growth target</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="15" s="20" customFormat="1" ht="48" customHeight="1">
-      <x:c r="A15" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">20</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" s="17" t="str">
-        <x:v>Actual growth from the older quarterly fee base</x:v>
-      </x:c>
-      <x:c r="C15" s="63" t="n">
-        <x:v>239400</x:v>
-      </x:c>
-      <x:c r="D15" s="63" t="n">
-        <x:v>268200</x:v>
-      </x:c>
-      <x:c r="E15" s="67"/>
-      <x:c r="F15" s="68" t="str">
-        <x:f>IFERROR(IF(E15="","",IF(NOT(IFERROR(ISFORMULA(E15),TRUE)),"Enter a formula",IF(ABS(E15-((D15-C15)/C15))&lt;0.000001,"Value OK; check refs/format","Try again"))),"Check formula / inputs")</x:f>
-      </x:c>
-      <x:c r="G15" s="71" t="str">
-        <x:v>Subtract old from new, divide by old. Percentage, 2 decimals.</x:v>
-      </x:c>
-      <x:c r="H15" s="72" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Percent change</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="16" s="20" customFormat="1" ht="48" customHeight="1">
-      <x:c r="A16" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">20</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B16" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Percents 3: Did actual beat the 12% target?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C16" s="15" t="n"/>
-      <x:c r="D16" s="15" t="n"/>
-      <x:c r="E16" s="5"/>
-      <x:c r="F16" s="68" t="str">
-        <x:f>IFERROR(IF(AND(LEFT(F14,8)="Value OK",LEFT(F15,8)="Value OK"),IF(E16="","",IF(OR(LOWER(TRIM(E16))=IF(D15&gt;E14,"yes","no"),LOWER(TRIM(E16))=IF(D15&gt;E14,"y","n")),"Reasoning OK; explain why","Compare the results")),"Complete E14, E15 first"),"Check earlier formulas")</x:f>
-        <x:v>Complete E14, E15 first</x:v>
-      </x:c>
-      <x:c r="G16" s="69" t="str">
-        <x:v>Compare actual fees in D15 with target E14; explain the dollar gap.</x:v>
-      </x:c>
-      <x:c r="H16" s="70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Interpret</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="18" s="20" customFormat="1" ht="16" customHeight="1">
-      <x:c r="A18" s="29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Prompt for Students</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="74" t="str">
-        <x:v>Value OK means the number is right and a formula is present. Inspect references (a formula can still hardcode inputs) and formatting. Complete E8, E12 and E16, then explain your conclusion to a partner.</x:v>
-      </x:c>
-      <x:c r="B20" s="75" t="n"/>
-      <x:c r="C20" s="75" t="n"/>
-      <x:c r="D20" s="75" t="n"/>
-      <x:c r="E20" s="75" t="n"/>
-      <x:c r="F20" s="75" t="n"/>
-      <x:c r="G20" s="75" t="n"/>
-      <x:c r="H20" s="76" t="n"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="77" t="n"/>
-      <x:c r="B21" s="78" t="n"/>
-      <x:c r="C21" s="78" t="n"/>
-      <x:c r="D21" s="78" t="n"/>
-      <x:c r="E21" s="78" t="n"/>
-      <x:c r="F21" s="78" t="n"/>
-      <x:c r="G21" s="78" t="n"/>
-      <x:c r="H21" s="79" t="n"/>
+    <x:row r="1" s="20" customFormat="1" ht="15" customHeight="1">
+      <x:c r="A1" s="101"/>
+      <x:c r="B1" s="101"/>
+      <x:c r="C1" s="101"/>
+      <x:c r="D1" s="101"/>
+      <x:c r="E1" s="101"/>
+      <x:c r="F1" s="101"/>
+      <x:c r="G1" s="101"/>
+      <x:c r="H1" s="101"/>
+    </x:row>
+    <x:row r="2" s="20" customFormat="1" ht="15" customHeight="1">
+      <x:c r="A2" s="101"/>
+      <x:c r="B2" s="101"/>
+      <x:c r="C2" s="101"/>
+      <x:c r="D2" s="101"/>
+      <x:c r="E2" s="101"/>
+      <x:c r="F2" s="101"/>
+      <x:c r="G2" s="101"/>
+      <x:c r="H2" s="101"/>
+    </x:row>
+    <x:row r="3" ht="15" customHeight="1">
+      <x:c r="A3" s="101"/>
+      <x:c r="B3" s="101"/>
+      <x:c r="C3" s="101"/>
+      <x:c r="D3" s="101"/>
+      <x:c r="E3" s="101"/>
+      <x:c r="F3" s="101"/>
+      <x:c r="G3" s="101"/>
+      <x:c r="H3" s="101"/>
+    </x:row>
+    <x:row r="4" ht="15" customHeight="1">
+      <x:c r="A4" s="101"/>
+      <x:c r="B4" s="101"/>
+      <x:c r="C4" s="101"/>
+      <x:c r="D4" s="101"/>
+      <x:c r="E4" s="101"/>
+      <x:c r="F4" s="101"/>
+      <x:c r="G4" s="101"/>
+      <x:c r="H4" s="101"/>
+    </x:row>
+    <x:row r="5" s="20" customFormat="1" ht="15" customHeight="1">
+      <x:c r="A5" s="101"/>
+      <x:c r="B5" s="101"/>
+      <x:c r="C5" s="101"/>
+      <x:c r="D5" s="101"/>
+      <x:c r="E5" s="101"/>
+      <x:c r="F5" s="101"/>
+      <x:c r="G5" s="101"/>
+      <x:c r="H5" s="101"/>
+    </x:row>
+    <x:row r="6" s="20" customFormat="1" ht="15" customHeight="1">
+      <x:c r="A6" s="101"/>
+      <x:c r="B6" s="101"/>
+      <x:c r="C6" s="101"/>
+      <x:c r="D6" s="101"/>
+      <x:c r="E6" s="101"/>
+      <x:c r="F6" s="101"/>
+      <x:c r="G6" s="101"/>
+      <x:c r="H6" s="101"/>
+    </x:row>
+    <x:row r="7" s="20" customFormat="1" ht="15" customHeight="1">
+      <x:c r="A7" s="101"/>
+      <x:c r="B7" s="101"/>
+      <x:c r="C7" s="101"/>
+      <x:c r="D7" s="101"/>
+      <x:c r="E7" s="101"/>
+      <x:c r="F7" s="101"/>
+      <x:c r="G7" s="101"/>
+      <x:c r="H7" s="101"/>
+    </x:row>
+    <x:row r="8" s="20" customFormat="1" ht="15" customHeight="1">
+      <x:c r="A8" s="101"/>
+      <x:c r="B8" s="101"/>
+      <x:c r="C8" s="101"/>
+      <x:c r="D8" s="101"/>
+      <x:c r="E8" s="101"/>
+      <x:c r="F8" s="101"/>
+      <x:c r="G8" s="101"/>
+      <x:c r="H8" s="101"/>
+    </x:row>
+    <x:row r="9" s="20" customFormat="1" ht="15" customHeight="1">
+      <x:c r="A9" s="101"/>
+      <x:c r="B9" s="101"/>
+      <x:c r="C9" s="101"/>
+      <x:c r="D9" s="101"/>
+      <x:c r="E9" s="101"/>
+      <x:c r="F9" s="101"/>
+      <x:c r="G9" s="101"/>
+      <x:c r="H9" s="101"/>
+    </x:row>
+    <x:row r="10" s="20" customFormat="1" ht="15" customHeight="1">
+      <x:c r="A10" s="101"/>
+      <x:c r="B10" s="101"/>
+      <x:c r="C10" s="101"/>
+      <x:c r="D10" s="101"/>
+      <x:c r="E10" s="101"/>
+      <x:c r="F10" s="101"/>
+      <x:c r="G10" s="101"/>
+      <x:c r="H10" s="101"/>
+    </x:row>
+    <x:row r="11" s="20" customFormat="1" ht="15" customHeight="1">
+      <x:c r="A11" s="101"/>
+      <x:c r="B11" s="101"/>
+      <x:c r="C11" s="101"/>
+      <x:c r="D11" s="101"/>
+      <x:c r="E11" s="101"/>
+      <x:c r="F11" s="101"/>
+      <x:c r="G11" s="101"/>
+      <x:c r="H11" s="101"/>
+    </x:row>
+    <x:row r="12" s="20" customFormat="1" ht="15" customHeight="1">
+      <x:c r="A12" s="101"/>
+      <x:c r="B12" s="101"/>
+      <x:c r="C12" s="101"/>
+      <x:c r="D12" s="101"/>
+      <x:c r="E12" s="101"/>
+      <x:c r="F12" s="101"/>
+      <x:c r="G12" s="101"/>
+      <x:c r="H12" s="101"/>
+    </x:row>
+    <x:row r="13" s="20" customFormat="1" ht="15" customHeight="1">
+      <x:c r="A13" s="101"/>
+      <x:c r="B13" s="101"/>
+      <x:c r="C13" s="101"/>
+      <x:c r="D13" s="101"/>
+      <x:c r="E13" s="101"/>
+      <x:c r="F13" s="101"/>
+      <x:c r="G13" s="101"/>
+      <x:c r="H13" s="101"/>
+    </x:row>
+    <x:row r="14" s="20" customFormat="1" ht="15" customHeight="1">
+      <x:c r="A14" s="101"/>
+      <x:c r="B14" s="101"/>
+      <x:c r="C14" s="101"/>
+      <x:c r="D14" s="101"/>
+      <x:c r="E14" s="101"/>
+      <x:c r="F14" s="101"/>
+      <x:c r="G14" s="101"/>
+      <x:c r="H14" s="101"/>
+    </x:row>
+    <x:row r="15" s="20" customFormat="1" ht="15" customHeight="1">
+      <x:c r="A15" s="101"/>
+      <x:c r="B15" s="101"/>
+      <x:c r="C15" s="101"/>
+      <x:c r="D15" s="101"/>
+      <x:c r="E15" s="101"/>
+      <x:c r="F15" s="101"/>
+      <x:c r="G15" s="101"/>
+      <x:c r="H15" s="101"/>
+    </x:row>
+    <x:row r="16" s="20" customFormat="1" ht="15" customHeight="1">
+      <x:c r="A16" s="101"/>
+      <x:c r="B16" s="101"/>
+      <x:c r="C16" s="101"/>
+      <x:c r="D16" s="101"/>
+      <x:c r="E16" s="101"/>
+      <x:c r="F16" s="101"/>
+      <x:c r="G16" s="101"/>
+      <x:c r="H16" s="101"/>
+    </x:row>
+    <x:row r="17" ht="15" customHeight="1">
+      <x:c r="A17" s="101"/>
+      <x:c r="B17" s="101"/>
+      <x:c r="C17" s="101"/>
+      <x:c r="D17" s="101"/>
+      <x:c r="E17" s="101"/>
+      <x:c r="F17" s="101"/>
+      <x:c r="G17" s="101"/>
+      <x:c r="H17" s="101"/>
+    </x:row>
+    <x:row r="18" s="20" customFormat="1" ht="15" customHeight="1">
+      <x:c r="A18" s="101"/>
+      <x:c r="B18" s="101"/>
+      <x:c r="C18" s="101"/>
+      <x:c r="D18" s="101"/>
+      <x:c r="E18" s="101"/>
+      <x:c r="F18" s="101"/>
+      <x:c r="G18" s="101"/>
+      <x:c r="H18" s="101"/>
+    </x:row>
+    <x:row r="19" ht="15" customHeight="1">
+      <x:c r="A19" s="101"/>
+      <x:c r="B19" s="101"/>
+      <x:c r="C19" s="101"/>
+      <x:c r="D19" s="101"/>
+      <x:c r="E19" s="101"/>
+      <x:c r="F19" s="101"/>
+      <x:c r="G19" s="101"/>
+      <x:c r="H19" s="101"/>
+    </x:row>
+    <x:row r="20" ht="15" customHeight="1">
+      <x:c r="A20" s="101"/>
+      <x:c r="B20" s="101"/>
+      <x:c r="C20" s="101"/>
+      <x:c r="D20" s="101"/>
+      <x:c r="E20" s="101"/>
+      <x:c r="F20" s="101"/>
+      <x:c r="G20" s="101"/>
+      <x:c r="H20" s="101"/>
+    </x:row>
+    <x:row r="21" ht="15" customHeight="1">
+      <x:c r="A21" s="101"/>
+      <x:c r="B21" s="101"/>
+      <x:c r="C21" s="101"/>
+      <x:c r="D21" s="101"/>
+      <x:c r="E21" s="101"/>
+      <x:c r="F21" s="101"/>
+      <x:c r="G21" s="101"/>
+      <x:c r="H21" s="101"/>
+    </x:row>
+    <x:row r="22" ht="15" customHeight="1">
+      <x:c r="A22" s="101"/>
+      <x:c r="B22" s="101"/>
+      <x:c r="C22" s="101"/>
+      <x:c r="D22" s="101"/>
+      <x:c r="E22" s="101"/>
+      <x:c r="F22" s="101"/>
+      <x:c r="G22" s="101"/>
+      <x:c r="H22" s="101"/>
+    </x:row>
+    <x:row r="23" ht="15" customHeight="1">
+      <x:c r="A23" s="101"/>
+      <x:c r="B23" s="101"/>
+      <x:c r="C23" s="101"/>
+      <x:c r="D23" s="101"/>
+      <x:c r="E23" s="101"/>
+      <x:c r="F23" s="101"/>
+      <x:c r="G23" s="101"/>
+      <x:c r="H23" s="101"/>
+    </x:row>
+    <x:row r="24" ht="15" customHeight="1">
+      <x:c r="A24" s="101"/>
+      <x:c r="B24" s="101"/>
+      <x:c r="C24" s="101"/>
+      <x:c r="D24" s="101"/>
+      <x:c r="E24" s="101"/>
+      <x:c r="F24" s="101"/>
+      <x:c r="G24" s="101"/>
+      <x:c r="H24" s="101"/>
+    </x:row>
+    <x:row r="25" ht="15" customHeight="1">
+      <x:c r="A25" s="101"/>
+      <x:c r="B25" s="101"/>
+      <x:c r="C25" s="101"/>
+      <x:c r="D25" s="101"/>
+      <x:c r="E25" s="101"/>
+      <x:c r="F25" s="101"/>
+      <x:c r="G25" s="101"/>
+      <x:c r="H25" s="101"/>
+    </x:row>
+    <x:row r="26" ht="15" customHeight="1">
+      <x:c r="A26" s="101"/>
+      <x:c r="B26" s="101"/>
+      <x:c r="C26" s="101"/>
+      <x:c r="D26" s="101"/>
+      <x:c r="E26" s="101"/>
+      <x:c r="F26" s="101"/>
+      <x:c r="G26" s="101"/>
+      <x:c r="H26" s="101"/>
+    </x:row>
+    <x:row r="27" ht="15" customHeight="1">
+      <x:c r="A27" s="101"/>
+      <x:c r="B27" s="101"/>
+      <x:c r="C27" s="101"/>
+      <x:c r="D27" s="101"/>
+      <x:c r="E27" s="101"/>
+      <x:c r="F27" s="101"/>
+      <x:c r="G27" s="101"/>
+      <x:c r="H27" s="101"/>
+    </x:row>
+    <x:row r="28" ht="15" customHeight="1">
+      <x:c r="A28" s="101"/>
+      <x:c r="B28" s="101"/>
+      <x:c r="C28" s="101"/>
+      <x:c r="D28" s="101"/>
+      <x:c r="E28" s="101"/>
+      <x:c r="F28" s="101"/>
+      <x:c r="G28" s="101"/>
+      <x:c r="H28" s="101"/>
+    </x:row>
+    <x:row r="29" ht="15" customHeight="1">
+      <x:c r="A29" s="101"/>
+      <x:c r="B29" s="101"/>
+      <x:c r="C29" s="101"/>
+      <x:c r="D29" s="101"/>
+      <x:c r="E29" s="101"/>
+      <x:c r="F29" s="101"/>
+      <x:c r="G29" s="101"/>
+      <x:c r="H29" s="101"/>
+    </x:row>
+    <x:row r="30" ht="15" customHeight="1">
+      <x:c r="A30" s="101"/>
+      <x:c r="B30" s="101"/>
+      <x:c r="C30" s="101"/>
+      <x:c r="D30" s="101"/>
+      <x:c r="E30" s="101"/>
+      <x:c r="F30" s="101"/>
+      <x:c r="G30" s="101"/>
+      <x:c r="H30" s="101"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A18:H18"/>
-    <x:mergeCell ref="A2:H2"/>
-    <x:mergeCell ref="A20:H21"/>
-    <x:mergeCell ref="A1:H1"/>
-  </x:mergeCells>
-  <x:conditionalFormatting sqref="F6:F16">
-    <x:cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Try again"/>
-    <x:cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Check formula"/>
-  </x:conditionalFormatting>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="E8 E12 E16">
-      <x:formula1>"yes,no"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>

--- a/MATH/M01/bus123-math-m01-l01-starter.xlsx
+++ b/MATH/M01/bus123-math-m01-l01-starter.xlsx
@@ -2,10 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rc890d777785a4ece" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R1684127f76a84c8e" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R1fcd9b2a988f41f3" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R61f1beff38ca42e1" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R0ab0b7f8e63441de" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Rd43c2cb0133e4a84" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R5e5876567b234b31" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R3c31cca81f7a449b" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Practice" sheetId="5" r:id="Raa4462b6aab544af"/>
   </x:sheets>
   <x:calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </x:workbook>
@@ -24,7 +25,7 @@
     <x:numFmt numFmtId="203" formatCode="0.00%"/>
     <x:numFmt numFmtId="204" formatCode="@"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -102,6 +103,12 @@
     </x:font>
     <x:font>
       <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
       <x:color theme="1"/>
       <x:name val="Aptos"/>
     </x:font>
@@ -224,7 +231,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="12">
+  <x:borders count="14">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -317,11 +324,27 @@
         <x:color rgb="FFE5E1D6"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="102">
+  <x:cellXfs count="109">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -572,6 +595,27 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1067,6 +1111,20 @@
       <x:c r="G19" s="23" t="n"/>
       <x:c r="H19" s="24" t="n"/>
     </x:row>
+    <x:row r="20" ht="40" customHeight="1">
+      <x:c r="A20" t="str">
+        <x:v>Reference Practice</x:v>
+      </x:c>
+      <x:c r="B20" s="73" t="str">
+        <x:v>Extra exercise: copy relative and absolute references, total service fees, and practice basic formatting.</x:v>
+      </x:c>
+      <x:c r="C20" s="73"/>
+      <x:c r="D20" s="73"/>
+      <x:c r="E20" s="73"/>
+      <x:c r="F20" s="73"/>
+      <x:c r="G20" s="73"/>
+      <x:c r="H20" s="73"/>
+    </x:row>
     <x:row r="22" s="20" customFormat="1" ht="24" customHeight="1">
       <x:c r="A22" s="27" t="inlineStr">
         <x:is>
@@ -1098,6 +1156,7 @@
     <x:mergeCell ref="B19:H19"/>
     <x:mergeCell ref="A22:H22"/>
     <x:mergeCell ref="A24:H25"/>
+    <x:mergeCell ref="B20:H20"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2436,4 +2495,300 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="102" t="str">
+        <x:v>Reference Practice: Service Fees</x:v>
+      </x:c>
+      <x:c r="B1" s="95"/>
+      <x:c r="C1" s="95"/>
+      <x:c r="D1" s="95"/>
+      <x:c r="E1" s="95"/>
+      <x:c r="F1" s="95"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="95" t="str">
+        <x:v>Meridian Advisory Group | Practice scenario | 8–10 minutes</x:v>
+      </x:c>
+      <x:c r="B2" s="95"/>
+      <x:c r="C2" s="95"/>
+      <x:c r="D2" s="95"/>
+      <x:c r="E2" s="95"/>
+      <x:c r="F2" s="95"/>
+    </x:row>
+    <x:row r="3" ht="23" customHeight="1">
+      <x:c r="A3" s="96"/>
+      <x:c r="B3" s="96"/>
+      <x:c r="C3" s="96"/>
+      <x:c r="D3" s="96"/>
+      <x:c r="E3" s="96"/>
+      <x:c r="F3" s="96"/>
+    </x:row>
+    <x:row r="4" ht="36" customHeight="1">
+      <x:c r="A4" s="95" t="str">
+        <x:v>1. Enter the data: Planning = 2 hours at $100/hour; Tax = 3 hours at $80/hour; Review = 4 hours at $75/hour.</x:v>
+      </x:c>
+      <x:c r="B4" s="95"/>
+      <x:c r="C4" s="95"/>
+      <x:c r="D4" s="95"/>
+      <x:c r="E4" s="95"/>
+      <x:c r="F4" s="95"/>
+    </x:row>
+    <x:row r="5" ht="32" customHeight="1">
+      <x:c r="A5" s="95" t="str">
+        <x:v>Type the hours in B16:B18 and hourly rates in C16:C18. Type 10% in B12.</x:v>
+      </x:c>
+      <x:c r="B5" s="95"/>
+      <x:c r="C5" s="95"/>
+      <x:c r="D5" s="95"/>
+      <x:c r="E5" s="95"/>
+      <x:c r="F5" s="95"/>
+    </x:row>
+    <x:row r="6" ht="34" customHeight="1">
+      <x:c r="A6" s="95" t="str">
+        <x:v>2. In D16, calculate hours × hourly rate with relative references. Copy your formula down to D18.</x:v>
+      </x:c>
+      <x:c r="B6" s="95"/>
+      <x:c r="C6" s="95"/>
+      <x:c r="D6" s="95"/>
+      <x:c r="E6" s="95"/>
+      <x:c r="F6" s="95"/>
+    </x:row>
+    <x:row r="7" ht="36" customHeight="1">
+      <x:c r="A7" s="95" t="str">
+        <x:v>3. In E16, calculate the discount amount. Keep B12 fixed with an absolute reference when copying down to E18.</x:v>
+      </x:c>
+      <x:c r="B7" s="95"/>
+      <x:c r="C7" s="95"/>
+      <x:c r="D7" s="95"/>
+      <x:c r="E7" s="95"/>
+      <x:c r="F7" s="95"/>
+    </x:row>
+    <x:row r="8" ht="34" customHeight="1">
+      <x:c r="A8" s="95" t="str">
+        <x:v>4. In F16, subtract the discount from the subtotal. Copy down to F18. Use SUM to total D19:F19.</x:v>
+      </x:c>
+      <x:c r="B8" s="95"/>
+      <x:c r="C8" s="95"/>
+      <x:c r="D8" s="95"/>
+      <x:c r="E8" s="95"/>
+      <x:c r="F8" s="95"/>
+    </x:row>
+    <x:row r="9" ht="40" customHeight="1">
+      <x:c r="A9" s="95" t="str">
+        <x:v>5. Format B12 as Percentage; C16:F19 as Currency (2 decimals). Bold and fill A15:F15; bold the totals. Adjust widths so labels fit.</x:v>
+      </x:c>
+      <x:c r="B9" s="95"/>
+      <x:c r="C9" s="95"/>
+      <x:c r="D9" s="95"/>
+      <x:c r="E9" s="95"/>
+      <x:c r="F9" s="95"/>
+    </x:row>
+    <x:row r="10" ht="38" customHeight="1">
+      <x:c r="A10" s="95" t="str">
+        <x:v>6. Change B12 to 20%. All three discount amounts and final fees should update. Restore 10%, answer the question below, and save.</x:v>
+      </x:c>
+      <x:c r="B10" s="95"/>
+      <x:c r="C10" s="95"/>
+      <x:c r="D10" s="95"/>
+      <x:c r="E10" s="95"/>
+      <x:c r="F10" s="95"/>
+    </x:row>
+    <x:row r="11" ht="23" customHeight="1">
+      <x:c r="A11" s="96"/>
+      <x:c r="B11" s="96"/>
+      <x:c r="C11" s="96"/>
+      <x:c r="D11" s="96"/>
+      <x:c r="E11" s="96"/>
+      <x:c r="F11" s="96"/>
+    </x:row>
+    <x:row r="12" ht="23" customHeight="1">
+      <x:c r="A12" s="96" t="str">
+        <x:v>Discount rate</x:v>
+      </x:c>
+      <x:c r="B12" s="96"/>
+      <x:c r="C12" s="96"/>
+      <x:c r="D12" s="96"/>
+      <x:c r="E12" s="96"/>
+      <x:c r="F12" s="96"/>
+    </x:row>
+    <x:row r="13" ht="23" customHeight="1">
+      <x:c r="A13" s="96"/>
+      <x:c r="B13" s="96"/>
+      <x:c r="C13" s="96"/>
+      <x:c r="D13" s="96"/>
+      <x:c r="E13" s="96"/>
+      <x:c r="F13" s="96"/>
+    </x:row>
+    <x:row r="14" ht="23" customHeight="1">
+      <x:c r="A14" s="96"/>
+      <x:c r="B14" s="96"/>
+      <x:c r="C14" s="96"/>
+      <x:c r="D14" s="96"/>
+      <x:c r="E14" s="96"/>
+      <x:c r="F14" s="96"/>
+    </x:row>
+    <x:row r="15" ht="23" customHeight="1">
+      <x:c r="A15" s="96" t="str">
+        <x:v>Service</x:v>
+      </x:c>
+      <x:c r="B15" s="96" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="C15" s="96" t="str">
+        <x:v>Hourly rate</x:v>
+      </x:c>
+      <x:c r="D15" s="96" t="str">
+        <x:v>Subtotal</x:v>
+      </x:c>
+      <x:c r="E15" s="96" t="str">
+        <x:v>Discount</x:v>
+      </x:c>
+      <x:c r="F15" s="96" t="str">
+        <x:v>Final fee</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="23" customHeight="1">
+      <x:c r="A16" s="96" t="str">
+        <x:v>Planning</x:v>
+      </x:c>
+      <x:c r="B16" s="96"/>
+      <x:c r="C16" s="96"/>
+      <x:c r="D16" s="96"/>
+      <x:c r="E16" s="96"/>
+      <x:c r="F16" s="96"/>
+    </x:row>
+    <x:row r="17" ht="23" customHeight="1">
+      <x:c r="A17" s="96" t="str">
+        <x:v>Tax</x:v>
+      </x:c>
+      <x:c r="B17" s="96"/>
+      <x:c r="C17" s="96"/>
+      <x:c r="D17" s="96"/>
+      <x:c r="E17" s="96"/>
+      <x:c r="F17" s="96"/>
+    </x:row>
+    <x:row r="18" ht="23" customHeight="1">
+      <x:c r="A18" s="96" t="str">
+        <x:v>Review</x:v>
+      </x:c>
+      <x:c r="B18" s="96"/>
+      <x:c r="C18" s="96"/>
+      <x:c r="D18" s="96"/>
+      <x:c r="E18" s="96"/>
+      <x:c r="F18" s="96"/>
+    </x:row>
+    <x:row r="19" ht="23" customHeight="1">
+      <x:c r="A19" s="96" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="B19" s="96"/>
+      <x:c r="C19" s="96"/>
+      <x:c r="D19" s="96"/>
+      <x:c r="E19" s="96"/>
+      <x:c r="F19" s="96"/>
+    </x:row>
+    <x:row r="20" ht="23" customHeight="1">
+      <x:c r="A20" s="96"/>
+      <x:c r="B20" s="96"/>
+      <x:c r="C20" s="96"/>
+      <x:c r="D20" s="96"/>
+      <x:c r="E20" s="96"/>
+      <x:c r="F20" s="96"/>
+    </x:row>
+    <x:row r="21" ht="23" customHeight="1">
+      <x:c r="A21" s="96"/>
+      <x:c r="B21" s="96"/>
+      <x:c r="C21" s="96"/>
+      <x:c r="D21" s="96"/>
+      <x:c r="E21" s="96"/>
+      <x:c r="F21" s="96"/>
+    </x:row>
+    <x:row r="22" ht="34" customHeight="1">
+      <x:c r="A22" s="95" t="str">
+        <x:v>Explain: When you copy E16 down to E17, which reference changes and which stays fixed? Why?</x:v>
+      </x:c>
+      <x:c r="B22" s="95"/>
+      <x:c r="C22" s="95"/>
+      <x:c r="D22" s="95"/>
+      <x:c r="E22" s="95"/>
+      <x:c r="F22" s="95"/>
+    </x:row>
+    <x:row r="23" ht="26" customHeight="1">
+      <x:c r="A23" s="103"/>
+      <x:c r="B23" s="104"/>
+      <x:c r="C23" s="104"/>
+      <x:c r="D23" s="104"/>
+      <x:c r="E23" s="104"/>
+      <x:c r="F23" s="105"/>
+    </x:row>
+    <x:row r="24" ht="26" customHeight="1">
+      <x:c r="A24" s="106"/>
+      <x:c r="B24" s="107"/>
+      <x:c r="C24" s="107"/>
+      <x:c r="D24" s="107"/>
+      <x:c r="E24" s="107"/>
+      <x:c r="F24" s="108"/>
+    </x:row>
+    <x:row r="25" ht="23" customHeight="1">
+      <x:c r="A25" s="96"/>
+      <x:c r="B25" s="96"/>
+      <x:c r="C25" s="96"/>
+      <x:c r="D25" s="96"/>
+      <x:c r="E25" s="96"/>
+      <x:c r="F25" s="96"/>
+    </x:row>
+    <x:row r="26" ht="23" customHeight="1">
+      <x:c r="A26" s="96"/>
+      <x:c r="B26" s="96"/>
+      <x:c r="C26" s="96"/>
+      <x:c r="D26" s="96"/>
+      <x:c r="E26" s="96"/>
+      <x:c r="F26" s="96"/>
+    </x:row>
+    <x:row r="27" ht="23" customHeight="1">
+      <x:c r="A27" s="96"/>
+      <x:c r="B27" s="96"/>
+      <x:c r="C27" s="96"/>
+      <x:c r="D27" s="96"/>
+      <x:c r="E27" s="96"/>
+      <x:c r="F27" s="96"/>
+    </x:row>
+    <x:row r="28" ht="23" customHeight="1">
+      <x:c r="A28" s="96"/>
+      <x:c r="B28" s="96"/>
+      <x:c r="C28" s="96"/>
+      <x:c r="D28" s="96"/>
+      <x:c r="E28" s="96"/>
+      <x:c r="F28" s="96"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A4:F4"/>
+    <x:mergeCell ref="A5:F5"/>
+    <x:mergeCell ref="A6:F6"/>
+    <x:mergeCell ref="A7:F7"/>
+    <x:mergeCell ref="A8:F8"/>
+    <x:mergeCell ref="A9:F9"/>
+    <x:mergeCell ref="A10:F10"/>
+    <x:mergeCell ref="A22:F22"/>
+    <x:mergeCell ref="A23:F24"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>